--- a/output/details/2026-06-03/preprocessed_data.xlsx
+++ b/output/details/2026-06-03/preprocessed_data.xlsx
@@ -15231,25 +15231,25 @@
         <v>46176</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1197184179445177</v>
+        <v>-0.127522507889844</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1278182216341252</v>
+        <v>-0.1470408119765692</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1276504213529732</v>
+        <v>-0.1467558019218599</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1134613547974028</v>
+        <v>-0.000269268837610324</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001694398239014256</v>
+        <v>0.001688383895110542</v>
       </c>
       <c r="G2" t="n">
-        <v>2.01195100319407</v>
+        <v>2.563877253920959</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4268096957665009</v>
+        <v>-0.2648664582870061</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
